--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/04_緊急連絡先一覧.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/04_緊急連絡先一覧.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,28 +26,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <i val="1"/>
+      <color rgb="005C665C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,16 +69,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFFAFE"/>
+        <fgColor rgb="00A9854A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -74,31 +92,73 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,158 +522,263 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>緊急連絡先一覧</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>利用者氏名：</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>作成日：　　年　　月　　日　 最終更新：　　年　　月　　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+          <t>事務所内に常時掲示。災害・急変時にすぐ参照できるようにする（個人情報の取扱いに注意）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>1. 関係機関</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>氏名・機関名</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>続柄・役割</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>電話番号（日中）</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>電話番号（夜間・緊急）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>家族①（緊急時最優先）</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr"/>
-      <c r="E4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>家族②</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>家族③</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>主治医・協力医療機関</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>主治医</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>救急（消防）</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>緊急対応病院</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>京都府 障害者支援課</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>075-414-4600</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>担当相談支援専門員</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>市町村 障害福祉担当</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>市区町村（障害福祉担当）</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>国保連（請求）</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>075-354-9070</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>事業所管理者（夜間）</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="6" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>地域包括／相談支援</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>警察</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>最寄り避難所</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="8" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2. 利用者・家族 緊急連絡</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>利用者氏名</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>緊急連絡先（続柄）</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>かかりつけ医・服薬等</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>※ 掲示・保管時は施錠管理。災害時持ち出し用に1部準備。年1回内容を更新。</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:E2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>